--- a/data/nzd0246/nzd0246.xlsx
+++ b/data/nzd0246/nzd0246.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q325"/>
+  <dimension ref="A1:Q326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18958,6 +18958,63 @@
         </is>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>341.71</v>
+      </c>
+      <c r="C326" t="n">
+        <v>354.44</v>
+      </c>
+      <c r="D326" t="n">
+        <v>378.59</v>
+      </c>
+      <c r="E326" t="n">
+        <v>372.71</v>
+      </c>
+      <c r="F326" t="n">
+        <v>372.54</v>
+      </c>
+      <c r="G326" t="n">
+        <v>366.36</v>
+      </c>
+      <c r="H326" t="n">
+        <v>373.44</v>
+      </c>
+      <c r="I326" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="J326" t="n">
+        <v>363.25</v>
+      </c>
+      <c r="K326" t="n">
+        <v>355.67</v>
+      </c>
+      <c r="L326" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="M326" t="n">
+        <v>363.19</v>
+      </c>
+      <c r="N326" t="n">
+        <v>367.09</v>
+      </c>
+      <c r="O326" t="n">
+        <v>363.55</v>
+      </c>
+      <c r="P326" t="n">
+        <v>377.46</v>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18969,7 +19026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B333"/>
+  <dimension ref="A1:B334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22302,6 +22359,16 @@
       </c>
       <c r="B333" t="n">
         <v>1.68</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -22470,28 +22537,28 @@
         <v>0.1147</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03005764340651115</v>
+        <v>-0.03023836399398179</v>
       </c>
       <c r="J2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001041552132865387</v>
+        <v>0.001060985929389413</v>
       </c>
       <c r="M2" t="n">
-        <v>5.285725729176838</v>
+        <v>5.270436359494509</v>
       </c>
       <c r="N2" t="n">
-        <v>49.86541222076158</v>
+        <v>49.71226837122911</v>
       </c>
       <c r="O2" t="n">
-        <v>7.061544605874948</v>
+        <v>7.0506927582493</v>
       </c>
       <c r="P2" t="n">
-        <v>342.8128220987617</v>
+        <v>342.814652437556</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22548,28 +22615,28 @@
         <v>0.1303</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07098089899530464</v>
+        <v>-0.06907028943162843</v>
       </c>
       <c r="J3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008813832735702909</v>
+        <v>0.008395572129557438</v>
       </c>
       <c r="M3" t="n">
-        <v>4.519567957502306</v>
+        <v>4.514502323544629</v>
       </c>
       <c r="N3" t="n">
-        <v>32.6059280361107</v>
+        <v>32.5378131352742</v>
       </c>
       <c r="O3" t="n">
-        <v>5.710160070970927</v>
+        <v>5.704192592757909</v>
       </c>
       <c r="P3" t="n">
-        <v>353.0592959189493</v>
+        <v>353.0399452580514</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22626,28 +22693,28 @@
         <v>0.0901</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05413365533072088</v>
+        <v>0.05734306154270569</v>
       </c>
       <c r="J4" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K4" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005075189747994369</v>
+        <v>0.005712652587039124</v>
       </c>
       <c r="M4" t="n">
-        <v>4.304504481722311</v>
+        <v>4.30609392818143</v>
       </c>
       <c r="N4" t="n">
-        <v>33.05946570627552</v>
+        <v>33.04863302044986</v>
       </c>
       <c r="O4" t="n">
-        <v>5.749736142317795</v>
+        <v>5.748794049228922</v>
       </c>
       <c r="P4" t="n">
-        <v>371.7051290346286</v>
+        <v>371.6726241563572</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22704,28 +22771,28 @@
         <v>0.1128</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03616596775333337</v>
+        <v>0.03904217773378756</v>
       </c>
       <c r="J5" t="n">
+        <v>325</v>
+      </c>
+      <c r="K5" t="n">
         <v>324</v>
       </c>
-      <c r="K5" t="n">
-        <v>323</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.00304614403437875</v>
+        <v>0.003560859625645008</v>
       </c>
       <c r="M5" t="n">
-        <v>3.385196975127219</v>
+        <v>3.385912184615077</v>
       </c>
       <c r="N5" t="n">
-        <v>24.3985932946867</v>
+        <v>24.39529006127228</v>
       </c>
       <c r="O5" t="n">
-        <v>4.939493222455792</v>
+        <v>4.939158841470102</v>
       </c>
       <c r="P5" t="n">
-        <v>366.9001946020476</v>
+        <v>366.8708482566985</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22782,28 +22849,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04679134342253852</v>
+        <v>0.05155434190542812</v>
       </c>
       <c r="J6" t="n">
+        <v>325</v>
+      </c>
+      <c r="K6" t="n">
         <v>324</v>
       </c>
-      <c r="K6" t="n">
-        <v>323</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.004292412093287123</v>
+        <v>0.00520458248384148</v>
       </c>
       <c r="M6" t="n">
-        <v>3.910879557588957</v>
+        <v>3.924762627426356</v>
       </c>
       <c r="N6" t="n">
-        <v>28.94685723895006</v>
+        <v>29.05496576987237</v>
       </c>
       <c r="O6" t="n">
-        <v>5.380228363085536</v>
+        <v>5.390265834805587</v>
       </c>
       <c r="P6" t="n">
-        <v>363.2690166415441</v>
+        <v>363.2204191471588</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22860,28 +22927,28 @@
         <v>0.1426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05184368607302108</v>
+        <v>0.05650980545499526</v>
       </c>
       <c r="J7" t="n">
+        <v>325</v>
+      </c>
+      <c r="K7" t="n">
         <v>324</v>
       </c>
-      <c r="K7" t="n">
-        <v>323</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.006859572513528422</v>
+        <v>0.008123405730661726</v>
       </c>
       <c r="M7" t="n">
-        <v>3.673826139079171</v>
+        <v>3.684960837599203</v>
       </c>
       <c r="N7" t="n">
-        <v>22.17917243641525</v>
+        <v>22.30021830145321</v>
       </c>
       <c r="O7" t="n">
-        <v>4.709476875027124</v>
+        <v>4.722310695142073</v>
       </c>
       <c r="P7" t="n">
-        <v>357.1221433618123</v>
+        <v>357.0745343375218</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22938,28 +23005,28 @@
         <v>0.0623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0806111707944763</v>
+        <v>0.0809612208952085</v>
       </c>
       <c r="J8" t="n">
+        <v>325</v>
+      </c>
+      <c r="K8" t="n">
         <v>324</v>
       </c>
-      <c r="K8" t="n">
-        <v>323</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01177610570600429</v>
+        <v>0.01195409372556377</v>
       </c>
       <c r="M8" t="n">
-        <v>4.138927385031331</v>
+        <v>4.128147935562787</v>
       </c>
       <c r="N8" t="n">
-        <v>31.080220870956</v>
+        <v>30.98536075671856</v>
       </c>
       <c r="O8" t="n">
-        <v>5.574963755124871</v>
+        <v>5.566449564733211</v>
       </c>
       <c r="P8" t="n">
-        <v>370.7244959590217</v>
+        <v>370.7209243522143</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23016,28 +23083,28 @@
         <v>0.0648</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1406289503406575</v>
+        <v>0.1407102002329471</v>
       </c>
       <c r="J9" t="n">
+        <v>325</v>
+      </c>
+      <c r="K9" t="n">
         <v>324</v>
       </c>
-      <c r="K9" t="n">
-        <v>323</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03881896338120061</v>
+        <v>0.03910739458868473</v>
       </c>
       <c r="M9" t="n">
-        <v>4.071738548877146</v>
+        <v>4.059558496268567</v>
       </c>
       <c r="N9" t="n">
-        <v>27.90941374830642</v>
+        <v>27.82333103946886</v>
       </c>
       <c r="O9" t="n">
-        <v>5.282936091635637</v>
+        <v>5.274782558501237</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2692966983604</v>
+        <v>366.2684676951184</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23094,28 +23161,28 @@
         <v>0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1665138495506573</v>
+        <v>0.1666553261295801</v>
       </c>
       <c r="J10" t="n">
+        <v>325</v>
+      </c>
+      <c r="K10" t="n">
         <v>324</v>
       </c>
-      <c r="K10" t="n">
-        <v>323</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.06324437026808849</v>
+        <v>0.06373435251689041</v>
       </c>
       <c r="M10" t="n">
-        <v>3.585206151115111</v>
+        <v>3.574782530996673</v>
       </c>
       <c r="N10" t="n">
-        <v>23.40696712044657</v>
+        <v>23.33489760226796</v>
       </c>
       <c r="O10" t="n">
-        <v>4.838074732829844</v>
+        <v>4.830620829900434</v>
       </c>
       <c r="P10" t="n">
-        <v>358.6134938494081</v>
+        <v>358.6120503454316</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23172,28 +23239,28 @@
         <v>0.0946</v>
       </c>
       <c r="I11" t="n">
-        <v>0.258226269970437</v>
+        <v>0.2587196794905295</v>
       </c>
       <c r="J11" t="n">
+        <v>325</v>
+      </c>
+      <c r="K11" t="n">
         <v>324</v>
       </c>
-      <c r="K11" t="n">
-        <v>323</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1214226810962581</v>
+        <v>0.1225247246357896</v>
       </c>
       <c r="M11" t="n">
-        <v>4.255603528597204</v>
+        <v>4.244891950899834</v>
       </c>
       <c r="N11" t="n">
-        <v>27.49925934252002</v>
+        <v>27.4165039967177</v>
       </c>
       <c r="O11" t="n">
-        <v>5.243973621455396</v>
+        <v>5.236077157254054</v>
       </c>
       <c r="P11" t="n">
-        <v>348.0190914871013</v>
+        <v>348.014057165451</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23250,28 +23317,28 @@
         <v>0.0968</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2971815776651156</v>
+        <v>0.2978434369397545</v>
       </c>
       <c r="J12" t="n">
+        <v>325</v>
+      </c>
+      <c r="K12" t="n">
         <v>324</v>
       </c>
-      <c r="K12" t="n">
-        <v>323</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1425898277048688</v>
+        <v>0.1439242671011975</v>
       </c>
       <c r="M12" t="n">
-        <v>4.405550007009843</v>
+        <v>4.394848085405355</v>
       </c>
       <c r="N12" t="n">
-        <v>30.26800791433689</v>
+        <v>30.17840080554689</v>
       </c>
       <c r="O12" t="n">
-        <v>5.501636839553925</v>
+        <v>5.493487126183776</v>
       </c>
       <c r="P12" t="n">
-        <v>347.2647086229384</v>
+        <v>347.2579555864848</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23328,28 +23395,28 @@
         <v>0.1069</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2848819071514657</v>
+        <v>0.2854751022659596</v>
       </c>
       <c r="J13" t="n">
+        <v>325</v>
+      </c>
+      <c r="K13" t="n">
         <v>324</v>
       </c>
-      <c r="K13" t="n">
-        <v>323</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.155365470896018</v>
+        <v>0.1567599395760227</v>
       </c>
       <c r="M13" t="n">
-        <v>3.954674129995538</v>
+        <v>3.945350605606151</v>
       </c>
       <c r="N13" t="n">
-        <v>25.1468763122781</v>
+        <v>25.07232511488154</v>
       </c>
       <c r="O13" t="n">
-        <v>5.014666121715193</v>
+        <v>5.007227288118799</v>
       </c>
       <c r="P13" t="n">
-        <v>354.673195428439</v>
+        <v>354.6671429813619</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23406,28 +23473,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>0.240723023137303</v>
+        <v>0.2396087090351182</v>
       </c>
       <c r="J14" t="n">
+        <v>325</v>
+      </c>
+      <c r="K14" t="n">
         <v>324</v>
       </c>
-      <c r="K14" t="n">
-        <v>323</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1258795458727858</v>
+        <v>0.1255275928851302</v>
       </c>
       <c r="M14" t="n">
-        <v>3.639547487538117</v>
+        <v>3.634514975889449</v>
       </c>
       <c r="N14" t="n">
-        <v>22.93460984949914</v>
+        <v>22.87463121211607</v>
       </c>
       <c r="O14" t="n">
-        <v>4.789009276405626</v>
+        <v>4.782743063568863</v>
       </c>
       <c r="P14" t="n">
-        <v>362.6179056453922</v>
+        <v>362.6292751374294</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23484,28 +23551,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.161714986790635</v>
+        <v>0.1599807392859676</v>
       </c>
       <c r="J15" t="n">
+        <v>325</v>
+      </c>
+      <c r="K15" t="n">
         <v>324</v>
       </c>
-      <c r="K15" t="n">
-        <v>323</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.05105312928929939</v>
+        <v>0.05028535773284171</v>
       </c>
       <c r="M15" t="n">
-        <v>4.022156811399647</v>
+        <v>4.019606776771075</v>
       </c>
       <c r="N15" t="n">
-        <v>27.70512114842918</v>
+        <v>27.64578851750437</v>
       </c>
       <c r="O15" t="n">
-        <v>5.263565440690291</v>
+        <v>5.257926256377544</v>
       </c>
       <c r="P15" t="n">
-        <v>362.207223380554</v>
+        <v>362.224918133906</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23562,28 +23629,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.210565980857499</v>
+        <v>1.209848020275714</v>
       </c>
       <c r="J16" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K16" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3592653401101958</v>
+        <v>0.3604900411958423</v>
       </c>
       <c r="M16" t="n">
-        <v>9.772380827837972</v>
+        <v>9.744960845064067</v>
       </c>
       <c r="N16" t="n">
-        <v>149.7192462622885</v>
+        <v>149.2588001391165</v>
       </c>
       <c r="O16" t="n">
-        <v>12.23598162234189</v>
+        <v>12.21715188327936</v>
       </c>
       <c r="P16" t="n">
-        <v>346.7264315373372</v>
+        <v>346.7337457820061</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23621,7 +23688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q325"/>
+  <dimension ref="A1:Q326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51843,6 +51910,93 @@
         </is>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-38.12389817997857,174.7334029205714</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-38.12358527193883,174.73421961509882</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-38.12319221638234,174.73495107044175</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-38.12280214175398,174.7356249420351</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-38.12231886327672,174.7362747151066</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-38.1218718626038,174.73697516177302</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-38.12133998279054,174.73757101321715</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-38.12087555320093,174.73824977229796</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-38.120433639511056,174.73895710982057</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-38.12000732965203,174.73968034901856</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-38.11953821130051,174.74035191910187</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-38.11902768752043,174.7409735674969</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>-38.118508382241004,174.74157170892698</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-38.11799920589261,174.74219119422304</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>-38.11738567134976,174.74266122977997</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0246/nzd0246.xlsx
+++ b/data/nzd0246/nzd0246.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q326"/>
+  <dimension ref="A1:Q327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19015,6 +19015,63 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>334.01</v>
+      </c>
+      <c r="C327" t="n">
+        <v>347.67</v>
+      </c>
+      <c r="D327" t="n">
+        <v>374.73</v>
+      </c>
+      <c r="E327" t="n">
+        <v>370.09</v>
+      </c>
+      <c r="F327" t="n">
+        <v>369.52</v>
+      </c>
+      <c r="G327" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="H327" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="I327" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="J327" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="K327" t="n">
+        <v>354.63</v>
+      </c>
+      <c r="L327" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="M327" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="N327" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="O327" t="n">
+        <v>363.68</v>
+      </c>
+      <c r="P327" t="n">
+        <v>363.44</v>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19026,7 +19083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B334"/>
+  <dimension ref="A1:B335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22369,6 +22426,16 @@
       </c>
       <c r="B334" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -22537,28 +22604,28 @@
         <v>0.1147</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03023836399398179</v>
+        <v>-0.03497076280400984</v>
       </c>
       <c r="J2" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K2" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001060985929389413</v>
+        <v>0.001422428763299899</v>
       </c>
       <c r="M2" t="n">
-        <v>5.270436359494509</v>
+        <v>5.279338590526967</v>
       </c>
       <c r="N2" t="n">
-        <v>49.71226837122911</v>
+        <v>49.75439799393678</v>
       </c>
       <c r="O2" t="n">
-        <v>7.0506927582493</v>
+        <v>7.053679748467234</v>
       </c>
       <c r="P2" t="n">
-        <v>342.814652437556</v>
+        <v>342.8629696771018</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22615,28 +22682,28 @@
         <v>0.1303</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06907028943162843</v>
+        <v>-0.07116026646907549</v>
       </c>
       <c r="J3" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K3" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008395572129557438</v>
+        <v>0.008955222081558079</v>
       </c>
       <c r="M3" t="n">
-        <v>4.514502323544629</v>
+        <v>4.512670729956789</v>
       </c>
       <c r="N3" t="n">
-        <v>32.5378131352742</v>
+        <v>32.47596252861555</v>
       </c>
       <c r="O3" t="n">
-        <v>5.704192592757909</v>
+        <v>5.698768509828729</v>
       </c>
       <c r="P3" t="n">
-        <v>353.0399452580514</v>
+        <v>353.0612836796886</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22693,28 +22760,28 @@
         <v>0.0901</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05734306154270569</v>
+        <v>0.05824742518860997</v>
       </c>
       <c r="J4" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K4" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005712652587039124</v>
+        <v>0.005930987998588044</v>
       </c>
       <c r="M4" t="n">
-        <v>4.30609392818143</v>
+        <v>4.297033261636706</v>
       </c>
       <c r="N4" t="n">
-        <v>33.04863302044986</v>
+        <v>32.9543642947049</v>
       </c>
       <c r="O4" t="n">
-        <v>5.748794049228922</v>
+        <v>5.740589194037916</v>
       </c>
       <c r="P4" t="n">
-        <v>371.6726241563572</v>
+        <v>371.6633907090782</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22771,28 +22838,28 @@
         <v>0.1128</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03904217773378756</v>
+        <v>0.04034225247080288</v>
       </c>
       <c r="J5" t="n">
+        <v>326</v>
+      </c>
+      <c r="K5" t="n">
         <v>325</v>
       </c>
-      <c r="K5" t="n">
-        <v>324</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.003560859625645008</v>
+        <v>0.003824127731043792</v>
       </c>
       <c r="M5" t="n">
-        <v>3.385912184615077</v>
+        <v>3.380440593936768</v>
       </c>
       <c r="N5" t="n">
-        <v>24.39529006127228</v>
+        <v>24.33471436396702</v>
       </c>
       <c r="O5" t="n">
-        <v>4.939158841470102</v>
+        <v>4.933022842433129</v>
       </c>
       <c r="P5" t="n">
-        <v>366.8708482566985</v>
+        <v>366.8574770885219</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22849,28 +22916,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05155434190542812</v>
+        <v>0.05449630069820773</v>
       </c>
       <c r="J6" t="n">
+        <v>326</v>
+      </c>
+      <c r="K6" t="n">
         <v>325</v>
       </c>
-      <c r="K6" t="n">
-        <v>324</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.00520458248384148</v>
+        <v>0.005835816574148556</v>
       </c>
       <c r="M6" t="n">
-        <v>3.924762627426356</v>
+        <v>3.928494273559633</v>
       </c>
       <c r="N6" t="n">
-        <v>29.05496576987237</v>
+        <v>29.03974932193801</v>
       </c>
       <c r="O6" t="n">
-        <v>5.390265834805587</v>
+        <v>5.388854175234101</v>
       </c>
       <c r="P6" t="n">
-        <v>363.2204191471588</v>
+        <v>363.1901613283837</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22927,28 +22994,28 @@
         <v>0.1426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05650980545499526</v>
+        <v>0.06087419364205589</v>
       </c>
       <c r="J7" t="n">
+        <v>326</v>
+      </c>
+      <c r="K7" t="n">
         <v>325</v>
       </c>
-      <c r="K7" t="n">
-        <v>324</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.008123405730661726</v>
+        <v>0.009408383854550006</v>
       </c>
       <c r="M7" t="n">
-        <v>3.684960837599203</v>
+        <v>3.694437684505399</v>
       </c>
       <c r="N7" t="n">
-        <v>22.30021830145321</v>
+        <v>22.39486254141113</v>
       </c>
       <c r="O7" t="n">
-        <v>4.722310695142073</v>
+        <v>4.732321052233368</v>
       </c>
       <c r="P7" t="n">
-        <v>357.0745343375218</v>
+        <v>357.0296469423781</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23005,28 +23072,28 @@
         <v>0.0623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0809612208952085</v>
+        <v>0.08112277078448965</v>
       </c>
       <c r="J8" t="n">
+        <v>326</v>
+      </c>
+      <c r="K8" t="n">
         <v>325</v>
       </c>
-      <c r="K8" t="n">
-        <v>324</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01195409372556377</v>
+        <v>0.01208058757204089</v>
       </c>
       <c r="M8" t="n">
-        <v>4.128147935562787</v>
+        <v>4.116349345820232</v>
       </c>
       <c r="N8" t="n">
-        <v>30.98536075671856</v>
+        <v>30.89024487546689</v>
       </c>
       <c r="O8" t="n">
-        <v>5.566449564733211</v>
+        <v>5.557899322178019</v>
       </c>
       <c r="P8" t="n">
-        <v>370.7209243522143</v>
+        <v>370.7192628240907</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23083,28 +23150,28 @@
         <v>0.0648</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1407102002329471</v>
+        <v>0.1389608167226334</v>
       </c>
       <c r="J9" t="n">
+        <v>326</v>
+      </c>
+      <c r="K9" t="n">
         <v>325</v>
       </c>
-      <c r="K9" t="n">
-        <v>324</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03910739458868473</v>
+        <v>0.03838886452037649</v>
       </c>
       <c r="M9" t="n">
-        <v>4.059558496268567</v>
+        <v>4.056781770821455</v>
       </c>
       <c r="N9" t="n">
-        <v>27.82333103946886</v>
+        <v>27.76395112855617</v>
       </c>
       <c r="O9" t="n">
-        <v>5.274782558501237</v>
+        <v>5.269150892559082</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2684676951184</v>
+        <v>366.2864599692974</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23161,28 +23228,28 @@
         <v>0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1666553261295801</v>
+        <v>0.1664817033392434</v>
       </c>
       <c r="J10" t="n">
+        <v>326</v>
+      </c>
+      <c r="K10" t="n">
         <v>325</v>
       </c>
-      <c r="K10" t="n">
-        <v>324</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.06373435251689041</v>
+        <v>0.0640081195569342</v>
       </c>
       <c r="M10" t="n">
-        <v>3.574782530996673</v>
+        <v>3.564786597548996</v>
       </c>
       <c r="N10" t="n">
-        <v>23.33489760226796</v>
+        <v>23.26335629044043</v>
       </c>
       <c r="O10" t="n">
-        <v>4.830620829900434</v>
+        <v>4.823210164448614</v>
       </c>
       <c r="P10" t="n">
-        <v>358.6120503454316</v>
+        <v>358.6138360424095</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23239,28 +23306,28 @@
         <v>0.0946</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2587196794905295</v>
+        <v>0.2585668506576086</v>
       </c>
       <c r="J11" t="n">
+        <v>326</v>
+      </c>
+      <c r="K11" t="n">
         <v>325</v>
       </c>
-      <c r="K11" t="n">
-        <v>324</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1225247246357896</v>
+        <v>0.123115695047646</v>
       </c>
       <c r="M11" t="n">
-        <v>4.244891950899834</v>
+        <v>4.232656977271675</v>
       </c>
       <c r="N11" t="n">
-        <v>27.4165039967177</v>
+        <v>27.33234571382695</v>
       </c>
       <c r="O11" t="n">
-        <v>5.236077157254054</v>
+        <v>5.228034593786364</v>
       </c>
       <c r="P11" t="n">
-        <v>348.014057165451</v>
+        <v>348.0156289981842</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23317,28 +23384,28 @@
         <v>0.0968</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2978434369397545</v>
+        <v>0.297721834399904</v>
       </c>
       <c r="J12" t="n">
+        <v>326</v>
+      </c>
+      <c r="K12" t="n">
         <v>325</v>
       </c>
-      <c r="K12" t="n">
-        <v>324</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1439242671011975</v>
+        <v>0.1446469891068365</v>
       </c>
       <c r="M12" t="n">
-        <v>4.394848085405355</v>
+        <v>4.382048175441486</v>
       </c>
       <c r="N12" t="n">
-        <v>30.17840080554689</v>
+        <v>30.08567092926717</v>
       </c>
       <c r="O12" t="n">
-        <v>5.493487126183776</v>
+        <v>5.485040649736989</v>
       </c>
       <c r="P12" t="n">
-        <v>347.2579555864848</v>
+        <v>347.2592062592075</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23395,28 +23462,28 @@
         <v>0.1069</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2854751022659596</v>
+        <v>0.286124859464164</v>
       </c>
       <c r="J13" t="n">
+        <v>326</v>
+      </c>
+      <c r="K13" t="n">
         <v>325</v>
       </c>
-      <c r="K13" t="n">
-        <v>324</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1567599395760227</v>
+        <v>0.158229696442879</v>
       </c>
       <c r="M13" t="n">
-        <v>3.945350605606151</v>
+        <v>3.936300878825577</v>
       </c>
       <c r="N13" t="n">
-        <v>25.07232511488154</v>
+        <v>24.99879806129146</v>
       </c>
       <c r="O13" t="n">
-        <v>5.007227288118799</v>
+        <v>4.999879804684454</v>
       </c>
       <c r="P13" t="n">
-        <v>354.6671429813619</v>
+        <v>354.6604602788036</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23473,28 +23540,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2396087090351182</v>
+        <v>0.2387495603436688</v>
       </c>
       <c r="J14" t="n">
+        <v>326</v>
+      </c>
+      <c r="K14" t="n">
         <v>325</v>
       </c>
-      <c r="K14" t="n">
-        <v>324</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1255275928851302</v>
+        <v>0.1254412235109552</v>
       </c>
       <c r="M14" t="n">
-        <v>3.634514975889449</v>
+        <v>3.628028297891529</v>
       </c>
       <c r="N14" t="n">
-        <v>22.87463121211607</v>
+        <v>22.81057433329862</v>
       </c>
       <c r="O14" t="n">
-        <v>4.782743063568863</v>
+        <v>4.776041701377681</v>
       </c>
       <c r="P14" t="n">
-        <v>362.6292751374294</v>
+        <v>362.6381114153102</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23551,28 +23618,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1599807392859676</v>
+        <v>0.1583115056747169</v>
       </c>
       <c r="J15" t="n">
+        <v>326</v>
+      </c>
+      <c r="K15" t="n">
         <v>325</v>
       </c>
-      <c r="K15" t="n">
-        <v>324</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.05028535773284171</v>
+        <v>0.04956584779081274</v>
       </c>
       <c r="M15" t="n">
-        <v>4.019606776771075</v>
+        <v>4.016672910345161</v>
       </c>
       <c r="N15" t="n">
-        <v>27.64578851750437</v>
+        <v>27.58460640903494</v>
       </c>
       <c r="O15" t="n">
-        <v>5.257926256377544</v>
+        <v>5.252104950306586</v>
       </c>
       <c r="P15" t="n">
-        <v>362.224918133906</v>
+        <v>362.2420860725686</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23629,28 +23696,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.209848020275714</v>
+        <v>1.200652822547993</v>
       </c>
       <c r="J16" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K16" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3604900411958423</v>
+        <v>0.3573846557323208</v>
       </c>
       <c r="M16" t="n">
-        <v>9.744960845064067</v>
+        <v>9.751889236201302</v>
       </c>
       <c r="N16" t="n">
-        <v>149.2588001391165</v>
+        <v>149.5268454035036</v>
       </c>
       <c r="O16" t="n">
-        <v>12.21715188327936</v>
+        <v>12.22811700154622</v>
       </c>
       <c r="P16" t="n">
-        <v>346.7337457820061</v>
+        <v>346.8281808040742</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23688,7 +23755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q326"/>
+  <dimension ref="A1:Q327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51997,6 +52064,93 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-38.12396436111692,174.73342927364155</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-38.1236434596578,174.73424278556368</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-38.123222494412076,174.73497273249265</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-38.12281942043873,174.73564530316276</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-38.12233834270481,174.73629876547648</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-38.121874831743824,174.73697882235544</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-38.12134192094761,174.73757339824402</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-38.12089526184014,174.7382740146461</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-38.120436900594385,174.73896104428164</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-38.120014238163115,174.73968836272383</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-38.119546657098205,174.7403615220945</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-38.11902671281183,174.74097238239838</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>-38.118505592509315,174.74156782898123</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-38.117998447012795,174.74219006484367</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>-38.11746751328853,174.7427830283766</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0246/nzd0246.xlsx
+++ b/data/nzd0246/nzd0246.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q327"/>
+  <dimension ref="A1:Q328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19072,6 +19072,63 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>331.66</v>
+      </c>
+      <c r="C328" t="n">
+        <v>344.36</v>
+      </c>
+      <c r="D328" t="n">
+        <v>371.83</v>
+      </c>
+      <c r="E328" t="n">
+        <v>366.94</v>
+      </c>
+      <c r="F328" t="n">
+        <v>366.64</v>
+      </c>
+      <c r="G328" t="n">
+        <v>363.26</v>
+      </c>
+      <c r="H328" t="n">
+        <v>374.79</v>
+      </c>
+      <c r="I328" t="n">
+        <v>371.62</v>
+      </c>
+      <c r="J328" t="n">
+        <v>365.37</v>
+      </c>
+      <c r="K328" t="n">
+        <v>358.42</v>
+      </c>
+      <c r="L328" t="n">
+        <v>360.47</v>
+      </c>
+      <c r="M328" t="n">
+        <v>369.12</v>
+      </c>
+      <c r="N328" t="n">
+        <v>374.35</v>
+      </c>
+      <c r="O328" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="P328" t="n">
+        <v>364.77</v>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19083,7 +19140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B335"/>
+  <dimension ref="A1:B336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22436,6 +22493,16 @@
       </c>
       <c r="B335" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -22604,28 +22671,28 @@
         <v>0.1147</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03497076280400984</v>
+        <v>-0.0410428764753191</v>
       </c>
       <c r="J2" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K2" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001422428763299899</v>
+        <v>0.001958758380738113</v>
       </c>
       <c r="M2" t="n">
-        <v>5.279338590526967</v>
+        <v>5.29497312700125</v>
       </c>
       <c r="N2" t="n">
-        <v>49.75439799393678</v>
+        <v>49.92166215397132</v>
       </c>
       <c r="O2" t="n">
-        <v>7.053679748467234</v>
+        <v>7.065526318256222</v>
       </c>
       <c r="P2" t="n">
-        <v>342.8629696771018</v>
+        <v>342.9252711164734</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22682,28 +22749,28 @@
         <v>0.1303</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07116026646907549</v>
+        <v>-0.07518097264731324</v>
       </c>
       <c r="J3" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K3" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008955222081558079</v>
+        <v>0.0100089049340808</v>
       </c>
       <c r="M3" t="n">
-        <v>4.512670729956789</v>
+        <v>4.521937170960808</v>
       </c>
       <c r="N3" t="n">
-        <v>32.47596252861555</v>
+        <v>32.51669815679048</v>
       </c>
       <c r="O3" t="n">
-        <v>5.698768509828729</v>
+        <v>5.702341462661674</v>
       </c>
       <c r="P3" t="n">
-        <v>353.0612836796886</v>
+        <v>353.1025371534794</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22760,28 +22827,28 @@
         <v>0.0901</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05824742518860997</v>
+        <v>0.05742423766906032</v>
       </c>
       <c r="J4" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K4" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005930987998588044</v>
+        <v>0.005802944317481962</v>
       </c>
       <c r="M4" t="n">
-        <v>4.297033261636706</v>
+        <v>4.288599869328237</v>
       </c>
       <c r="N4" t="n">
-        <v>32.9543642947049</v>
+        <v>32.85945695531125</v>
       </c>
       <c r="O4" t="n">
-        <v>5.740589194037916</v>
+        <v>5.73231689243636</v>
       </c>
       <c r="P4" t="n">
-        <v>371.6633907090782</v>
+        <v>371.6718368235807</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22838,28 +22905,28 @@
         <v>0.1128</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04034225247080288</v>
+        <v>0.03974677424812861</v>
       </c>
       <c r="J5" t="n">
+        <v>327</v>
+      </c>
+      <c r="K5" t="n">
         <v>326</v>
       </c>
-      <c r="K5" t="n">
-        <v>325</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.003824127731043792</v>
+        <v>0.003736955796321273</v>
       </c>
       <c r="M5" t="n">
-        <v>3.380440593936768</v>
+        <v>3.373908793011403</v>
       </c>
       <c r="N5" t="n">
-        <v>24.33471436396702</v>
+        <v>24.26309777770373</v>
       </c>
       <c r="O5" t="n">
-        <v>4.933022842433129</v>
+        <v>4.925758599211266</v>
       </c>
       <c r="P5" t="n">
-        <v>366.8574770885219</v>
+        <v>366.8636314976588</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22916,28 +22983,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05449630069820773</v>
+        <v>0.05568790263432912</v>
       </c>
       <c r="J6" t="n">
+        <v>327</v>
+      </c>
+      <c r="K6" t="n">
         <v>326</v>
       </c>
-      <c r="K6" t="n">
-        <v>325</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.005835816574148556</v>
+        <v>0.006130514271564524</v>
       </c>
       <c r="M6" t="n">
-        <v>3.928494273559633</v>
+        <v>3.92297539822468</v>
       </c>
       <c r="N6" t="n">
-        <v>29.03974932193801</v>
+        <v>28.9628025840706</v>
       </c>
       <c r="O6" t="n">
-        <v>5.388854175234101</v>
+        <v>5.381710005571705</v>
       </c>
       <c r="P6" t="n">
-        <v>363.1901613283837</v>
+        <v>363.1778458388091</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22994,28 +23061,28 @@
         <v>0.1426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06087419364205589</v>
+        <v>0.06361923550033939</v>
       </c>
       <c r="J7" t="n">
+        <v>327</v>
+      </c>
+      <c r="K7" t="n">
         <v>326</v>
       </c>
-      <c r="K7" t="n">
-        <v>325</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.009408383854550006</v>
+        <v>0.01030621918150176</v>
       </c>
       <c r="M7" t="n">
-        <v>3.694437684505399</v>
+        <v>3.6963688719496</v>
       </c>
       <c r="N7" t="n">
-        <v>22.39486254141113</v>
+        <v>22.39055047488756</v>
       </c>
       <c r="O7" t="n">
-        <v>4.732321052233368</v>
+        <v>4.731865432880309</v>
       </c>
       <c r="P7" t="n">
-        <v>357.0296469423781</v>
+        <v>357.0012762815368</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23072,28 +23139,28 @@
         <v>0.0623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08112277078448965</v>
+        <v>0.08225955845608324</v>
       </c>
       <c r="J8" t="n">
+        <v>327</v>
+      </c>
+      <c r="K8" t="n">
         <v>326</v>
       </c>
-      <c r="K8" t="n">
-        <v>325</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01208058757204089</v>
+        <v>0.01249555125631008</v>
       </c>
       <c r="M8" t="n">
-        <v>4.116349345820232</v>
+        <v>4.109997581604228</v>
       </c>
       <c r="N8" t="n">
-        <v>30.89024487546689</v>
+        <v>30.80653126473203</v>
       </c>
       <c r="O8" t="n">
-        <v>5.557899322178019</v>
+        <v>5.550363165121002</v>
       </c>
       <c r="P8" t="n">
-        <v>370.7192628240907</v>
+        <v>370.707513852984</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23150,28 +23217,28 @@
         <v>0.0648</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1389608167226334</v>
+        <v>0.1399290584985233</v>
       </c>
       <c r="J9" t="n">
+        <v>327</v>
+      </c>
+      <c r="K9" t="n">
         <v>326</v>
       </c>
-      <c r="K9" t="n">
-        <v>325</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03838886452037649</v>
+        <v>0.03914596082910859</v>
       </c>
       <c r="M9" t="n">
-        <v>4.056781770821455</v>
+        <v>4.048891754157943</v>
       </c>
       <c r="N9" t="n">
-        <v>27.76395112855617</v>
+        <v>27.6867958923053</v>
       </c>
       <c r="O9" t="n">
-        <v>5.269150892559082</v>
+        <v>5.261824388204656</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2864599692974</v>
+        <v>366.2764529601317</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23228,28 +23295,28 @@
         <v>0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1664817033392434</v>
+        <v>0.1678604200846774</v>
       </c>
       <c r="J10" t="n">
+        <v>327</v>
+      </c>
+      <c r="K10" t="n">
         <v>326</v>
       </c>
-      <c r="K10" t="n">
-        <v>325</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0640081195569342</v>
+        <v>0.06537029369053049</v>
       </c>
       <c r="M10" t="n">
-        <v>3.564786597548996</v>
+        <v>3.560025463649601</v>
       </c>
       <c r="N10" t="n">
-        <v>23.26335629044043</v>
+        <v>23.20823790786147</v>
       </c>
       <c r="O10" t="n">
-        <v>4.823210164448614</v>
+        <v>4.817492906882321</v>
       </c>
       <c r="P10" t="n">
-        <v>358.6138360424095</v>
+        <v>358.599586676753</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23306,28 +23373,28 @@
         <v>0.0946</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2585668506576086</v>
+        <v>0.2606575415802424</v>
       </c>
       <c r="J11" t="n">
+        <v>327</v>
+      </c>
+      <c r="K11" t="n">
         <v>326</v>
       </c>
-      <c r="K11" t="n">
-        <v>325</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.123115695047646</v>
+        <v>0.1254508767438579</v>
       </c>
       <c r="M11" t="n">
-        <v>4.232656977271675</v>
+        <v>4.229812600334975</v>
       </c>
       <c r="N11" t="n">
-        <v>27.33234571382695</v>
+        <v>27.28585140478326</v>
       </c>
       <c r="O11" t="n">
-        <v>5.228034593786364</v>
+        <v>5.223586067519445</v>
       </c>
       <c r="P11" t="n">
-        <v>348.0156289981842</v>
+        <v>347.9940212099783</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23384,28 +23451,28 @@
         <v>0.0968</v>
       </c>
       <c r="I12" t="n">
-        <v>0.297721834399904</v>
+        <v>0.3008615373271299</v>
       </c>
       <c r="J12" t="n">
+        <v>327</v>
+      </c>
+      <c r="K12" t="n">
         <v>326</v>
       </c>
-      <c r="K12" t="n">
-        <v>325</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1446469891068365</v>
+        <v>0.1477546181482992</v>
       </c>
       <c r="M12" t="n">
-        <v>4.382048175441486</v>
+        <v>4.382147657883853</v>
       </c>
       <c r="N12" t="n">
-        <v>30.08567092926717</v>
+        <v>30.07761149786283</v>
       </c>
       <c r="O12" t="n">
-        <v>5.485040649736989</v>
+        <v>5.484305926720611</v>
       </c>
       <c r="P12" t="n">
-        <v>347.2592062592075</v>
+        <v>347.2267566823014</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23462,28 +23529,28 @@
         <v>0.1069</v>
       </c>
       <c r="I13" t="n">
-        <v>0.286124859464164</v>
+        <v>0.2901950792127634</v>
       </c>
       <c r="J13" t="n">
+        <v>327</v>
+      </c>
+      <c r="K13" t="n">
         <v>326</v>
       </c>
-      <c r="K13" t="n">
-        <v>325</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.158229696442879</v>
+        <v>0.1621722816025389</v>
       </c>
       <c r="M13" t="n">
-        <v>3.936300878825577</v>
+        <v>3.943318895963919</v>
       </c>
       <c r="N13" t="n">
-        <v>24.99879806129146</v>
+        <v>25.06366616736705</v>
       </c>
       <c r="O13" t="n">
-        <v>4.999879804684454</v>
+        <v>5.006362568508902</v>
       </c>
       <c r="P13" t="n">
-        <v>354.6604602788036</v>
+        <v>354.6183935891141</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23540,28 +23607,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2387495603436688</v>
+        <v>0.2419320943933181</v>
       </c>
       <c r="J14" t="n">
+        <v>327</v>
+      </c>
+      <c r="K14" t="n">
         <v>326</v>
       </c>
-      <c r="K14" t="n">
-        <v>325</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1254412235109552</v>
+        <v>0.1287028285459727</v>
       </c>
       <c r="M14" t="n">
-        <v>3.628028297891529</v>
+        <v>3.632146502004075</v>
       </c>
       <c r="N14" t="n">
-        <v>22.81057433329862</v>
+        <v>22.82714486004605</v>
       </c>
       <c r="O14" t="n">
-        <v>4.776041701377681</v>
+        <v>4.777776141684126</v>
       </c>
       <c r="P14" t="n">
-        <v>362.6381114153102</v>
+        <v>362.6052191685613</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23618,28 +23685,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1583115056747169</v>
+        <v>0.1620303159359329</v>
       </c>
       <c r="J15" t="n">
+        <v>327</v>
+      </c>
+      <c r="K15" t="n">
         <v>326</v>
       </c>
-      <c r="K15" t="n">
-        <v>325</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.04956584779081274</v>
+        <v>0.05191938797052209</v>
       </c>
       <c r="M15" t="n">
-        <v>4.016672910345161</v>
+        <v>4.021621478030564</v>
       </c>
       <c r="N15" t="n">
-        <v>27.58460640903494</v>
+        <v>27.61815552223231</v>
       </c>
       <c r="O15" t="n">
-        <v>5.252104950306586</v>
+        <v>5.255297852855946</v>
       </c>
       <c r="P15" t="n">
-        <v>362.2420860725686</v>
+        <v>362.2036512835559</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23696,28 +23763,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.200652822547993</v>
+        <v>1.192259380496108</v>
       </c>
       <c r="J16" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K16" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3573846557323208</v>
+        <v>0.3547736350244629</v>
       </c>
       <c r="M16" t="n">
-        <v>9.751889236201302</v>
+        <v>9.75559117395677</v>
       </c>
       <c r="N16" t="n">
-        <v>149.5268454035036</v>
+        <v>149.6717878770278</v>
       </c>
       <c r="O16" t="n">
-        <v>12.22811700154622</v>
+        <v>12.23404217243949</v>
       </c>
       <c r="P16" t="n">
-        <v>346.8281808040742</v>
+        <v>346.9148077575791</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23755,7 +23822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q327"/>
+  <dimension ref="A1:Q328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52151,6 +52218,93 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-38.123984559254986,174.73343731647154</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-38.12367190889488,174.73425411412103</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-38.12324524215162,174.73498900710246</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-38.12284019442489,174.73566978315725</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-38.12235691910811,174.73632170094044</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-38.12189187202327,174.73699983092143</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-38.121331261083064,174.73756028059788</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-38.120865860425575,174.73823784983648</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-38.120419812516225,174.73894042770954</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-38.11998906195163,174.73965915893976</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-38.1195097905147,174.74031960428573</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-38.11898915403082,174.74092671662603</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>-38.11846435298149,174.74151047329573</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-38.11794579240095,174.74211170334746</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>-38.11745974940137,174.74277147400454</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0246/nzd0246.xlsx
+++ b/data/nzd0246/nzd0246.xlsx
@@ -19140,7 +19140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B336"/>
+  <dimension ref="A1:B337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22503,6 +22503,16 @@
       </c>
       <c r="B336" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0246/nzd0246.xlsx
+++ b/data/nzd0246/nzd0246.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q328"/>
+  <dimension ref="A1:Q331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19129,6 +19129,177 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>332.9</v>
+      </c>
+      <c r="C329" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="D329" t="n">
+        <v>372.15</v>
+      </c>
+      <c r="E329" t="n">
+        <v>367.02</v>
+      </c>
+      <c r="F329" t="n">
+        <v>368.17</v>
+      </c>
+      <c r="G329" t="n">
+        <v>363.72</v>
+      </c>
+      <c r="H329" t="n">
+        <v>377.08</v>
+      </c>
+      <c r="I329" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="J329" t="n">
+        <v>366.04</v>
+      </c>
+      <c r="K329" t="n">
+        <v>359.34</v>
+      </c>
+      <c r="L329" t="n">
+        <v>361.02</v>
+      </c>
+      <c r="M329" t="n">
+        <v>369.64</v>
+      </c>
+      <c r="N329" t="n">
+        <v>374.09</v>
+      </c>
+      <c r="O329" t="n">
+        <v>373.7</v>
+      </c>
+      <c r="P329" t="n">
+        <v>372.16</v>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="C330" t="n">
+        <v>343.95</v>
+      </c>
+      <c r="D330" t="n">
+        <v>367.74</v>
+      </c>
+      <c r="E330" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="F330" t="n">
+        <v>364.47</v>
+      </c>
+      <c r="G330" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="H330" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="I330" t="n">
+        <v>368.38</v>
+      </c>
+      <c r="J330" t="n">
+        <v>363.85</v>
+      </c>
+      <c r="K330" t="n">
+        <v>357.05</v>
+      </c>
+      <c r="L330" t="n">
+        <v>359.2</v>
+      </c>
+      <c r="M330" t="n">
+        <v>368.79</v>
+      </c>
+      <c r="N330" t="n">
+        <v>375.02</v>
+      </c>
+      <c r="O330" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="P330" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>335.08</v>
+      </c>
+      <c r="C331" t="n">
+        <v>346.3</v>
+      </c>
+      <c r="D331" t="n">
+        <v>370.29</v>
+      </c>
+      <c r="E331" t="n">
+        <v>366.16</v>
+      </c>
+      <c r="F331" t="n">
+        <v>367.36</v>
+      </c>
+      <c r="G331" t="n">
+        <v>363.88</v>
+      </c>
+      <c r="H331" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="I331" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="J331" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="K331" t="n">
+        <v>358.57</v>
+      </c>
+      <c r="L331" t="n">
+        <v>360.86</v>
+      </c>
+      <c r="M331" t="n">
+        <v>369.88</v>
+      </c>
+      <c r="N331" t="n">
+        <v>376.03</v>
+      </c>
+      <c r="O331" t="n">
+        <v>376.8</v>
+      </c>
+      <c r="P331" t="n">
+        <v>382.89</v>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19140,7 +19311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B337"/>
+  <dimension ref="A1:B340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22513,6 +22684,36 @@
       </c>
       <c r="B337" t="n">
         <v>-0.01</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>
@@ -22681,28 +22882,28 @@
         <v>0.1147</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0410428764753191</v>
+        <v>-0.05617310916688392</v>
       </c>
       <c r="J2" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K2" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001958758380738113</v>
+        <v>0.003685759610798089</v>
       </c>
       <c r="M2" t="n">
-        <v>5.29497312700125</v>
+        <v>5.326980475862598</v>
       </c>
       <c r="N2" t="n">
-        <v>49.92166215397132</v>
+        <v>50.15377616899028</v>
       </c>
       <c r="O2" t="n">
-        <v>7.065526318256222</v>
+        <v>7.081933081369118</v>
       </c>
       <c r="P2" t="n">
-        <v>342.9252711164734</v>
+        <v>343.0814022908835</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22759,28 +22960,28 @@
         <v>0.1303</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07518097264731324</v>
+        <v>-0.08518173244799634</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K3" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0100089049340808</v>
+        <v>0.01294923129192371</v>
       </c>
       <c r="M3" t="n">
-        <v>4.521937170960808</v>
+        <v>4.53726654796216</v>
       </c>
       <c r="N3" t="n">
-        <v>32.51669815679048</v>
+        <v>32.52114451490771</v>
       </c>
       <c r="O3" t="n">
-        <v>5.702341462661674</v>
+        <v>5.702731320596097</v>
       </c>
       <c r="P3" t="n">
-        <v>353.1025371534794</v>
+        <v>353.2057420605583</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22837,28 +23038,28 @@
         <v>0.0901</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05742423766906032</v>
+        <v>0.05192757429452664</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K4" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005802944317481962</v>
+        <v>0.004828514081635982</v>
       </c>
       <c r="M4" t="n">
-        <v>4.288599869328237</v>
+        <v>4.281207783304768</v>
       </c>
       <c r="N4" t="n">
-        <v>32.85945695531125</v>
+        <v>32.67818102002669</v>
       </c>
       <c r="O4" t="n">
-        <v>5.73231689243636</v>
+        <v>5.716483273834245</v>
       </c>
       <c r="P4" t="n">
-        <v>371.6718368235807</v>
+        <v>371.7285733760456</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22915,28 +23116,28 @@
         <v>0.1128</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03974677424812861</v>
+        <v>0.03604878363036421</v>
       </c>
       <c r="J5" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K5" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003736955796321273</v>
+        <v>0.003131657647763797</v>
       </c>
       <c r="M5" t="n">
-        <v>3.373908793011403</v>
+        <v>3.366571509377271</v>
       </c>
       <c r="N5" t="n">
-        <v>24.26309777770373</v>
+        <v>24.09281095033064</v>
       </c>
       <c r="O5" t="n">
-        <v>4.925758599211266</v>
+        <v>4.90844282337389</v>
       </c>
       <c r="P5" t="n">
-        <v>366.8636314976588</v>
+        <v>366.9020768539855</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22993,28 +23194,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05568790263432912</v>
+        <v>0.05919908038722401</v>
       </c>
       <c r="J6" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K6" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006130514271564524</v>
+        <v>0.007047843258867981</v>
       </c>
       <c r="M6" t="n">
-        <v>3.92297539822468</v>
+        <v>3.908114772723836</v>
       </c>
       <c r="N6" t="n">
-        <v>28.9628025840706</v>
+        <v>28.75707594208422</v>
       </c>
       <c r="O6" t="n">
-        <v>5.381710005571705</v>
+        <v>5.362562441788834</v>
       </c>
       <c r="P6" t="n">
-        <v>363.1778458388091</v>
+        <v>363.1413522537006</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23071,28 +23272,28 @@
         <v>0.1426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06361923550033939</v>
+        <v>0.0714584418816991</v>
       </c>
       <c r="J7" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K7" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01030621918150176</v>
+        <v>0.01312049083305311</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6963688719496</v>
+        <v>3.700028215838601</v>
       </c>
       <c r="N7" t="n">
-        <v>22.39055047488756</v>
+        <v>22.36989015080998</v>
       </c>
       <c r="O7" t="n">
-        <v>4.731865432880309</v>
+        <v>4.729681823422161</v>
       </c>
       <c r="P7" t="n">
-        <v>357.0012762815368</v>
+        <v>356.9197874194348</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23149,28 +23350,28 @@
         <v>0.0623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08225955845608324</v>
+        <v>0.08436910788827752</v>
       </c>
       <c r="J8" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K8" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01249555125631008</v>
+        <v>0.01337660067857049</v>
       </c>
       <c r="M8" t="n">
-        <v>4.109997581604228</v>
+        <v>4.088224505406481</v>
       </c>
       <c r="N8" t="n">
-        <v>30.80653126473203</v>
+        <v>30.5784367701694</v>
       </c>
       <c r="O8" t="n">
-        <v>5.550363165121002</v>
+        <v>5.529777280340448</v>
       </c>
       <c r="P8" t="n">
-        <v>370.707513852984</v>
+        <v>370.6856116177711</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23227,28 +23428,28 @@
         <v>0.0648</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1399290584985233</v>
+        <v>0.1421438877493962</v>
       </c>
       <c r="J9" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K9" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03914596082910859</v>
+        <v>0.04105087213400416</v>
       </c>
       <c r="M9" t="n">
-        <v>4.048891754157943</v>
+        <v>4.032480905713354</v>
       </c>
       <c r="N9" t="n">
-        <v>27.6867958923053</v>
+        <v>27.48984408097677</v>
       </c>
       <c r="O9" t="n">
-        <v>5.261824388204656</v>
+        <v>5.243075822546987</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2764529601317</v>
+        <v>366.2534379649875</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23305,28 +23506,28 @@
         <v>0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1678604200846774</v>
+        <v>0.1715133059140608</v>
       </c>
       <c r="J10" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K10" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06537029369053049</v>
+        <v>0.06920679282884834</v>
       </c>
       <c r="M10" t="n">
-        <v>3.560025463649601</v>
+        <v>3.544328404802696</v>
       </c>
       <c r="N10" t="n">
-        <v>23.20823790786147</v>
+        <v>23.04320241254242</v>
       </c>
       <c r="O10" t="n">
-        <v>4.817492906882321</v>
+        <v>4.800333573049109</v>
       </c>
       <c r="P10" t="n">
-        <v>358.599586676753</v>
+        <v>358.5616175509755</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23383,28 +23584,28 @@
         <v>0.0946</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2606575415802424</v>
+        <v>0.2665207315174425</v>
       </c>
       <c r="J11" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K11" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1254508767438579</v>
+        <v>0.1322582809887117</v>
       </c>
       <c r="M11" t="n">
-        <v>4.229812600334975</v>
+        <v>4.219078285327645</v>
       </c>
       <c r="N11" t="n">
-        <v>27.28585140478326</v>
+        <v>27.14390423789256</v>
       </c>
       <c r="O11" t="n">
-        <v>5.223586067519445</v>
+        <v>5.209981212815701</v>
       </c>
       <c r="P11" t="n">
-        <v>347.9940212099783</v>
+        <v>347.9330784477866</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23461,28 +23662,28 @@
         <v>0.0968</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3008615373271299</v>
+        <v>0.3097707947594562</v>
       </c>
       <c r="J12" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K12" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1477546181482992</v>
+        <v>0.1568762003601337</v>
       </c>
       <c r="M12" t="n">
-        <v>4.382147657883853</v>
+        <v>4.379724853840147</v>
       </c>
       <c r="N12" t="n">
-        <v>30.07761149786283</v>
+        <v>30.03709609589812</v>
       </c>
       <c r="O12" t="n">
-        <v>5.484305926720611</v>
+        <v>5.48061092360132</v>
       </c>
       <c r="P12" t="n">
-        <v>347.2267566823014</v>
+        <v>347.134146735002</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23539,28 +23740,28 @@
         <v>0.1069</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2901950792127634</v>
+        <v>0.3025637674802009</v>
       </c>
       <c r="J13" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K13" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1621722816025389</v>
+        <v>0.1742002770640636</v>
       </c>
       <c r="M13" t="n">
-        <v>3.943318895963919</v>
+        <v>3.96473445743742</v>
       </c>
       <c r="N13" t="n">
-        <v>25.06366616736705</v>
+        <v>25.27565665017476</v>
       </c>
       <c r="O13" t="n">
-        <v>5.006362568508902</v>
+        <v>5.027490094487979</v>
       </c>
       <c r="P13" t="n">
-        <v>354.6183935891141</v>
+        <v>354.4898208040696</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23617,28 +23818,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2419320943933181</v>
+        <v>0.2523976838704682</v>
       </c>
       <c r="J14" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K14" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1287028285459727</v>
+        <v>0.1392305592789096</v>
       </c>
       <c r="M14" t="n">
-        <v>3.632146502004075</v>
+        <v>3.648721719810121</v>
       </c>
       <c r="N14" t="n">
-        <v>22.82714486004605</v>
+        <v>22.93853724720006</v>
       </c>
       <c r="O14" t="n">
-        <v>4.777776141684126</v>
+        <v>4.789419301669051</v>
       </c>
       <c r="P14" t="n">
-        <v>362.6052191685613</v>
+        <v>362.496418798465</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23695,28 +23896,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1620303159359329</v>
+        <v>0.1761847979879421</v>
       </c>
       <c r="J15" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K15" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05191938797052209</v>
+        <v>0.06072836877957644</v>
       </c>
       <c r="M15" t="n">
-        <v>4.021621478030564</v>
+        <v>4.053955617343859</v>
       </c>
       <c r="N15" t="n">
-        <v>27.61815552223231</v>
+        <v>27.96270446053078</v>
       </c>
       <c r="O15" t="n">
-        <v>5.255297852855946</v>
+        <v>5.287977350606826</v>
       </c>
       <c r="P15" t="n">
-        <v>362.2036512835559</v>
+        <v>362.056498275726</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23773,28 +23974,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.192259380496108</v>
+        <v>1.190030182746763</v>
       </c>
       <c r="J16" t="n">
+        <v>330</v>
+      </c>
+      <c r="K16" t="n">
         <v>327</v>
       </c>
-      <c r="K16" t="n">
-        <v>324</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.3547736350244629</v>
+        <v>0.3582254064292503</v>
       </c>
       <c r="M16" t="n">
-        <v>9.75559117395677</v>
+        <v>9.699538020297743</v>
       </c>
       <c r="N16" t="n">
-        <v>149.6717878770278</v>
+        <v>148.4875345366565</v>
       </c>
       <c r="O16" t="n">
-        <v>12.23404217243949</v>
+        <v>12.18554613206386</v>
       </c>
       <c r="P16" t="n">
-        <v>346.9148077575791</v>
+        <v>346.9378852054498</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23832,7 +24033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q328"/>
+  <dimension ref="A1:Q331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52315,6 +52516,267 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-38.123973901514134,174.7334330725947</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-38.12365953218768,174.73424918568406</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-38.12324273205633,174.73498721128294</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-38.122839666831666,174.73566916144293</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-38.12234705039446,174.73630951647374</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-38.12188890288396,174.73699617033728</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-38.12131646648056,174.73754207490143</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-38.12085429371195,174.73822362236987</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-38.12041544266354,174.73893515553428</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-38.11998295057456,174.73965206989763</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-38.11950610385546,174.7403154125072</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-38.11898577503919,174.74092260828894</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>-38.11846592978751,174.74151266630605</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-38.11793995485741,174.74210301582707</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>-38.11741661018688,174.74270727344017</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-38.12398636419495,174.73343803519273</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-38.1236754328184,174.7342555173569</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-38.12327732430401,174.7350119599317</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-38.12285760499952,174.73569029973478</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-38.1223709159088,174.73633898218313</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-38.121900650347484,174.73701065351986</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-38.121345151209276,174.73757737328904</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-38.12088679681871,174.73826360235725</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-38.120429726210894,174.73895238846777</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-38.11999816258834,174.73966971545042</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>-38.11951830334542,174.7403292834851</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>-38.118991298390796,174.74092932384016</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>-38.11846028967345,174.74150482207727</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-38.11794228987491,174.74210649083506</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>-38.11738397846944,174.742658710411</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-38.12395516451764,174.73342561158856</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-38.123655234719855,174.73424747442166</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-38.12325732198465,174.73499764948565</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-38.122845338458696,174.73567584487233</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-38.12235227500774,174.73631596707335</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-38.12188787013982,174.73699489709065</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-38.121345151209276,174.73757737328904</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-38.120862887974205,174.73823419361557</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-38.120417986309164,174.73893822441232</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>-38.119988065531494,174.7396580031176</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-38.11950717633817,174.7403166319336</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-38.11898421550455,174.74092071213352</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-38.118454164387664,174.74149630307747</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-38.11792185846814,174.74207608452258</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>-38.11735397361564,174.7426140567871</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0246/nzd0246.xlsx
+++ b/data/nzd0246/nzd0246.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q331"/>
+  <dimension ref="A1:Q332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19268,7 +19268,7 @@
         <v>363.88</v>
       </c>
       <c r="H331" t="n">
-        <v>372.64</v>
+        <v>376.49</v>
       </c>
       <c r="I331" t="n">
         <v>372.08</v>
@@ -19297,6 +19297,63 @@
       <c r="Q331" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>337.14</v>
+      </c>
+      <c r="C332" t="n">
+        <v>347.09</v>
+      </c>
+      <c r="D332" t="n">
+        <v>369.46</v>
+      </c>
+      <c r="E332" t="n">
+        <v>366.06</v>
+      </c>
+      <c r="F332" t="n">
+        <v>366.28</v>
+      </c>
+      <c r="G332" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="H332" t="n">
+        <v>378.18</v>
+      </c>
+      <c r="I332" t="n">
+        <v>372.19</v>
+      </c>
+      <c r="J332" t="n">
+        <v>366.7</v>
+      </c>
+      <c r="K332" t="n">
+        <v>357.8</v>
+      </c>
+      <c r="L332" t="n">
+        <v>360.84</v>
+      </c>
+      <c r="M332" t="n">
+        <v>369.32</v>
+      </c>
+      <c r="N332" t="n">
+        <v>376.7</v>
+      </c>
+      <c r="O332" t="n">
+        <v>376.49</v>
+      </c>
+      <c r="P332" t="n">
+        <v>389.23</v>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19311,7 +19368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B340"/>
+  <dimension ref="A1:B341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22714,6 +22771,16 @@
       </c>
       <c r="B340" t="n">
         <v>1.61</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -22882,28 +22949,28 @@
         <v>0.1147</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05617310916688392</v>
+        <v>-0.05874319267540035</v>
       </c>
       <c r="J2" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K2" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003685759610798089</v>
+        <v>0.004051222176571501</v>
       </c>
       <c r="M2" t="n">
-        <v>5.326980475862598</v>
+        <v>5.324728575802709</v>
       </c>
       <c r="N2" t="n">
-        <v>50.15377616899028</v>
+        <v>50.061033747911</v>
       </c>
       <c r="O2" t="n">
-        <v>7.081933081369118</v>
+        <v>7.075382233343369</v>
       </c>
       <c r="P2" t="n">
-        <v>343.0814022908835</v>
+        <v>343.1080289438642</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22960,28 +23027,28 @@
         <v>0.1303</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08518173244799634</v>
+        <v>-0.08739854507615911</v>
       </c>
       <c r="J3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01294923129192371</v>
+        <v>0.01369357704223673</v>
       </c>
       <c r="M3" t="n">
-        <v>4.53726654796216</v>
+        <v>4.536239769034476</v>
       </c>
       <c r="N3" t="n">
-        <v>32.52114451490771</v>
+        <v>32.46662436688946</v>
       </c>
       <c r="O3" t="n">
-        <v>5.702731320596097</v>
+        <v>5.697949136916673</v>
       </c>
       <c r="P3" t="n">
-        <v>353.2057420605583</v>
+        <v>353.228708746418</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23038,28 +23105,28 @@
         <v>0.0901</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05192757429452664</v>
+        <v>0.04980318548869531</v>
       </c>
       <c r="J4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004828514081635982</v>
+        <v>0.004467090996489786</v>
       </c>
       <c r="M4" t="n">
-        <v>4.281207783304768</v>
+        <v>4.280669141242288</v>
       </c>
       <c r="N4" t="n">
-        <v>32.67818102002669</v>
+        <v>32.6196159686384</v>
       </c>
       <c r="O4" t="n">
-        <v>5.716483273834245</v>
+        <v>5.711358504650045</v>
       </c>
       <c r="P4" t="n">
-        <v>371.7285733760456</v>
+        <v>371.7505825299667</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23116,28 +23183,28 @@
         <v>0.1128</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03604878363036421</v>
+        <v>0.03498652293224989</v>
       </c>
       <c r="J5" t="n">
+        <v>331</v>
+      </c>
+      <c r="K5" t="n">
         <v>330</v>
       </c>
-      <c r="K5" t="n">
-        <v>329</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.003131657647763797</v>
+        <v>0.002968718967266359</v>
       </c>
       <c r="M5" t="n">
-        <v>3.366571509377271</v>
+        <v>3.363055170848903</v>
       </c>
       <c r="N5" t="n">
-        <v>24.09281095033064</v>
+        <v>24.02970702734039</v>
       </c>
       <c r="O5" t="n">
-        <v>4.90844282337389</v>
+        <v>4.902010508693387</v>
       </c>
       <c r="P5" t="n">
-        <v>366.9020768539855</v>
+        <v>366.9131616435712</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23194,28 +23261,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05919908038722401</v>
+        <v>0.06010525095589633</v>
       </c>
       <c r="J6" t="n">
+        <v>331</v>
+      </c>
+      <c r="K6" t="n">
         <v>330</v>
       </c>
-      <c r="K6" t="n">
-        <v>329</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.007047843258867981</v>
+        <v>0.007309874039520659</v>
       </c>
       <c r="M6" t="n">
-        <v>3.908114772723836</v>
+        <v>3.901308521568961</v>
       </c>
       <c r="N6" t="n">
-        <v>28.75707594208422</v>
+        <v>28.67714094954007</v>
       </c>
       <c r="O6" t="n">
-        <v>5.362562441788834</v>
+        <v>5.355104195955488</v>
       </c>
       <c r="P6" t="n">
-        <v>363.1413522537006</v>
+        <v>363.1318962791923</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23272,28 +23339,28 @@
         <v>0.1426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0714584418816991</v>
+        <v>0.07396784262330953</v>
       </c>
       <c r="J7" t="n">
+        <v>331</v>
+      </c>
+      <c r="K7" t="n">
         <v>330</v>
       </c>
-      <c r="K7" t="n">
-        <v>329</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01312049083305311</v>
+        <v>0.01410275442092745</v>
       </c>
       <c r="M7" t="n">
-        <v>3.700028215838601</v>
+        <v>3.700981631004157</v>
       </c>
       <c r="N7" t="n">
-        <v>22.36989015080998</v>
+        <v>22.35737579624922</v>
       </c>
       <c r="O7" t="n">
-        <v>4.729681823422161</v>
+        <v>4.728358678891568</v>
       </c>
       <c r="P7" t="n">
-        <v>356.9197874194348</v>
+        <v>356.8936015883518</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23350,28 +23417,28 @@
         <v>0.0623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08436910788827752</v>
+        <v>0.08966384190908946</v>
       </c>
       <c r="J8" t="n">
+        <v>331</v>
+      </c>
+      <c r="K8" t="n">
         <v>330</v>
       </c>
-      <c r="K8" t="n">
-        <v>329</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01337660067857049</v>
+        <v>0.01512340290171821</v>
       </c>
       <c r="M8" t="n">
-        <v>4.088224505406481</v>
+        <v>4.104810176185743</v>
       </c>
       <c r="N8" t="n">
-        <v>30.5784367701694</v>
+        <v>30.6037182632318</v>
       </c>
       <c r="O8" t="n">
-        <v>5.529777280340448</v>
+        <v>5.532062749393918</v>
       </c>
       <c r="P8" t="n">
-        <v>370.6856116177711</v>
+        <v>370.6304286691799</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23428,28 +23495,28 @@
         <v>0.0648</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1421438877493962</v>
+        <v>0.1433825615095565</v>
       </c>
       <c r="J9" t="n">
+        <v>331</v>
+      </c>
+      <c r="K9" t="n">
         <v>330</v>
       </c>
-      <c r="K9" t="n">
-        <v>329</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.04105087213400416</v>
+        <v>0.04198596687903644</v>
       </c>
       <c r="M9" t="n">
-        <v>4.032480905713354</v>
+        <v>4.026169326833783</v>
       </c>
       <c r="N9" t="n">
-        <v>27.48984408097677</v>
+        <v>27.42000906618604</v>
       </c>
       <c r="O9" t="n">
-        <v>5.243075822546987</v>
+        <v>5.236411850321367</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2534379649875</v>
+        <v>366.2405122886248</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23506,28 +23573,28 @@
         <v>0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1715133059140608</v>
+        <v>0.1735756003024285</v>
       </c>
       <c r="J10" t="n">
+        <v>331</v>
+      </c>
+      <c r="K10" t="n">
         <v>330</v>
       </c>
-      <c r="K10" t="n">
-        <v>329</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.06920679282884834</v>
+        <v>0.07109300218068804</v>
       </c>
       <c r="M10" t="n">
-        <v>3.544328404802696</v>
+        <v>3.543321262534588</v>
       </c>
       <c r="N10" t="n">
-        <v>23.04320241254242</v>
+        <v>23.01070605877246</v>
       </c>
       <c r="O10" t="n">
-        <v>4.800333573049109</v>
+        <v>4.796947577238307</v>
       </c>
       <c r="P10" t="n">
-        <v>358.5616175509755</v>
+        <v>358.5400973164423</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23584,28 +23651,28 @@
         <v>0.0946</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2665207315174425</v>
+        <v>0.2680995464522095</v>
       </c>
       <c r="J11" t="n">
+        <v>331</v>
+      </c>
+      <c r="K11" t="n">
         <v>330</v>
       </c>
-      <c r="K11" t="n">
-        <v>329</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1322582809887117</v>
+        <v>0.134296122638413</v>
       </c>
       <c r="M11" t="n">
-        <v>4.219078285327645</v>
+        <v>4.213705574542473</v>
       </c>
       <c r="N11" t="n">
-        <v>27.14390423789256</v>
+        <v>27.083529460222</v>
       </c>
       <c r="O11" t="n">
-        <v>5.209981212815701</v>
+        <v>5.204183841893174</v>
       </c>
       <c r="P11" t="n">
-        <v>347.9330784477866</v>
+        <v>347.9166033665022</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23662,28 +23729,28 @@
         <v>0.0968</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3097707947594562</v>
+        <v>0.3129141429752013</v>
       </c>
       <c r="J12" t="n">
+        <v>331</v>
+      </c>
+      <c r="K12" t="n">
         <v>330</v>
       </c>
-      <c r="K12" t="n">
-        <v>329</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1568762003601337</v>
+        <v>0.1600684163771605</v>
       </c>
       <c r="M12" t="n">
-        <v>4.379724853840147</v>
+        <v>4.379552941938392</v>
       </c>
       <c r="N12" t="n">
-        <v>30.03709609589812</v>
+        <v>30.03280262323495</v>
       </c>
       <c r="O12" t="n">
-        <v>5.48061092360132</v>
+        <v>5.480219213063922</v>
       </c>
       <c r="P12" t="n">
-        <v>347.134146735002</v>
+        <v>347.1013456028243</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23740,28 +23807,28 @@
         <v>0.1069</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3025637674802009</v>
+        <v>0.3064788644599081</v>
       </c>
       <c r="J13" t="n">
+        <v>331</v>
+      </c>
+      <c r="K13" t="n">
         <v>330</v>
       </c>
-      <c r="K13" t="n">
-        <v>329</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1742002770640636</v>
+        <v>0.1781223534351486</v>
       </c>
       <c r="M13" t="n">
-        <v>3.96473445743742</v>
+        <v>3.971014037652846</v>
       </c>
       <c r="N13" t="n">
-        <v>25.27565665017476</v>
+        <v>25.33360626729601</v>
       </c>
       <c r="O13" t="n">
-        <v>5.027490094487979</v>
+        <v>5.033250070014007</v>
       </c>
       <c r="P13" t="n">
-        <v>354.4898208040696</v>
+        <v>354.4489664014689</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23818,28 +23885,28 @@
         <v>0.1045</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2523976838704682</v>
+        <v>0.2567345865149037</v>
       </c>
       <c r="J14" t="n">
+        <v>331</v>
+      </c>
+      <c r="K14" t="n">
         <v>330</v>
       </c>
-      <c r="K14" t="n">
-        <v>329</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1392305592789096</v>
+        <v>0.1432962955118166</v>
       </c>
       <c r="M14" t="n">
-        <v>3.648721719810121</v>
+        <v>3.65810465110583</v>
       </c>
       <c r="N14" t="n">
-        <v>22.93853724720006</v>
+        <v>23.03412149868259</v>
       </c>
       <c r="O14" t="n">
-        <v>4.789419301669051</v>
+        <v>4.799387617048929</v>
       </c>
       <c r="P14" t="n">
-        <v>362.496418798465</v>
+        <v>362.4511628143619</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23896,28 +23963,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1761847979879421</v>
+        <v>0.1818512551173853</v>
       </c>
       <c r="J15" t="n">
+        <v>331</v>
+      </c>
+      <c r="K15" t="n">
         <v>330</v>
       </c>
-      <c r="K15" t="n">
-        <v>329</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.06072836877957644</v>
+        <v>0.06423572413604339</v>
       </c>
       <c r="M15" t="n">
-        <v>4.053955617343859</v>
+        <v>4.069359726876917</v>
       </c>
       <c r="N15" t="n">
-        <v>27.96270446053078</v>
+        <v>28.15980580030781</v>
       </c>
       <c r="O15" t="n">
-        <v>5.287977350606826</v>
+        <v>5.306581366596371</v>
       </c>
       <c r="P15" t="n">
-        <v>362.056498275726</v>
+        <v>361.9973682664094</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23974,28 +24041,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.190030182746763</v>
+        <v>1.196040003479847</v>
       </c>
       <c r="J16" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K16" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3582254064292503</v>
+        <v>0.3615751490075143</v>
       </c>
       <c r="M16" t="n">
-        <v>9.699538020297743</v>
+        <v>9.708091714476589</v>
       </c>
       <c r="N16" t="n">
-        <v>148.4875345366565</v>
+        <v>148.3541836077816</v>
       </c>
       <c r="O16" t="n">
-        <v>12.18554613206386</v>
+        <v>12.18007321849017</v>
       </c>
       <c r="P16" t="n">
-        <v>346.9378852054498</v>
+        <v>346.875253803379</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24033,7 +24100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q331"/>
+  <dimension ref="A1:Q332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52728,7 +52795,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>-38.121345151209276,174.73757737328904</t>
+          <t>-38.121320278190666,174.73754676545136</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -52774,6 +52841,93 @@
       <c r="Q331" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>-38.12393745891486,174.73341856128366</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>-38.1236484447206,174.73424477062744</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-38.123263832543714,174.7350023073947</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-38.12284599795021,174.73567662201535</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-38.122359241158186,174.73632456787425</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-38.121892711127835,174.73700086543442</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-38.12130935990186,174.73753332980968</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-38.1208621771706,174.7382333193019</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-38.12041113803232,174.73892996204876</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-38.119993180488066,174.73966393633845</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-38.1195073103985,174.74031678436194</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-38.11898785441868,174.74092513649634</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-38.11845010107889,174.74149065186057</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-38.11792366810736,174.74207877765244</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>-38.11731696371281,174.74255897824276</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
